--- a/00-esmagadora-modelo/dados_sujos/apontamentos_mensais/producao_2025_11.xlsx
+++ b/00-esmagadora-modelo/dados_sujos/apontamentos_mensais/producao_2025_11.xlsx
@@ -480,25 +480,25 @@
         <v>45962</v>
       </c>
       <c r="B5" t="n">
-        <v>1327.18</v>
+        <v>1414.06</v>
       </c>
       <c r="C5" t="n">
-        <v>22.88</v>
+        <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>966.11</v>
+        <v>1031.04</v>
       </c>
       <c r="E5" t="n">
-        <v>264.79</v>
+        <v>291.85</v>
       </c>
       <c r="F5" t="n">
-        <v>1752</v>
+        <v>1408</v>
       </c>
       <c r="G5" t="n">
-        <v>327161</v>
+        <v>375695</v>
       </c>
       <c r="H5" t="n">
-        <v>60827</v>
+        <v>64084</v>
       </c>
     </row>
     <row r="6">
@@ -506,25 +506,25 @@
         <v>45963</v>
       </c>
       <c r="B6" t="n">
-        <v>576.16</v>
+        <v>396.08</v>
       </c>
       <c r="C6" t="n">
-        <v>9.210000000000001</v>
+        <v>6.35</v>
       </c>
       <c r="D6" t="n">
-        <v>420.73</v>
+        <v>286.5</v>
       </c>
       <c r="E6" t="n">
-        <v>117.5</v>
+        <v>78.05</v>
       </c>
       <c r="F6" t="n">
-        <v>1033</v>
+        <v>494</v>
       </c>
       <c r="G6" t="n">
-        <v>164240</v>
+        <v>116115</v>
       </c>
       <c r="H6" t="n">
-        <v>25842</v>
+        <v>18346</v>
       </c>
     </row>
     <row r="7">
@@ -532,25 +532,25 @@
         <v>45964</v>
       </c>
       <c r="B7" t="n">
-        <v>720.89</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>11.68</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>522.95</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>141.8</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1357</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>208807</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>33795</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -558,25 +558,25 @@
         <v>45965</v>
       </c>
       <c r="B8" t="n">
-        <v>958.61</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>15.53</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>696.96</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>193.39</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1842</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>264504</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>46751</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -584,25 +584,25 @@
         <v>45966</v>
       </c>
       <c r="B9" t="n">
-        <v>1043.88</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>16.6</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>755.3200000000001</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>205.25</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>2212</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>288132</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>48493</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -610,25 +610,25 @@
         <v>45967</v>
       </c>
       <c r="B10" t="n">
-        <v>716.78</v>
+        <v>1473.13</v>
       </c>
       <c r="C10" t="n">
-        <v>11.47</v>
+        <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>511.52</v>
+        <v>1070.12</v>
       </c>
       <c r="E10" t="n">
-        <v>139.46</v>
+        <v>289.57</v>
       </c>
       <c r="F10" t="n">
-        <v>1377</v>
+        <v>1555</v>
       </c>
       <c r="G10" t="n">
-        <v>201543</v>
+        <v>408543</v>
       </c>
       <c r="H10" t="n">
-        <v>33757</v>
+        <v>67339</v>
       </c>
     </row>
     <row r="11">
@@ -636,25 +636,25 @@
         <v>45968</v>
       </c>
       <c r="B11" t="n">
-        <v>521.46</v>
+        <v>1493.9</v>
       </c>
       <c r="C11" t="n">
-        <v>8.119999999999999</v>
+        <v>24</v>
       </c>
       <c r="D11" t="n">
-        <v>374</v>
+        <v>1078.31</v>
       </c>
       <c r="E11" t="n">
-        <v>103.14</v>
+        <v>293.82</v>
       </c>
       <c r="F11" t="n">
-        <v>876</v>
+        <v>1370</v>
       </c>
       <c r="G11" t="n">
-        <v>153649</v>
+        <v>409560</v>
       </c>
       <c r="H11" t="n">
-        <v>23787</v>
+        <v>67993</v>
       </c>
     </row>
     <row r="12">
@@ -662,25 +662,25 @@
         <v>45969</v>
       </c>
       <c r="B12" t="n">
-        <v>1452.12</v>
+        <v>1473.48</v>
       </c>
       <c r="C12" t="n">
         <v>24</v>
       </c>
       <c r="D12" t="n">
-        <v>1058.87</v>
+        <v>1067.84</v>
       </c>
       <c r="E12" t="n">
-        <v>288.64</v>
+        <v>292.55</v>
       </c>
       <c r="F12" t="n">
-        <v>1978</v>
+        <v>1270</v>
       </c>
       <c r="G12" t="n">
-        <v>419501</v>
+        <v>384885</v>
       </c>
       <c r="H12" t="n">
-        <v>63834</v>
+        <v>71140</v>
       </c>
     </row>
     <row r="13">
@@ -688,25 +688,25 @@
         <v>45970</v>
       </c>
       <c r="B13" t="n">
-        <v>854.62</v>
+        <v>1298.97</v>
       </c>
       <c r="C13" t="n">
-        <v>13.07</v>
+        <v>21.39</v>
       </c>
       <c r="D13" t="n">
-        <v>614.23</v>
+        <v>937.54</v>
       </c>
       <c r="E13" t="n">
-        <v>170.17</v>
+        <v>257.82</v>
       </c>
       <c r="F13" t="n">
-        <v>1571</v>
+        <v>1445</v>
       </c>
       <c r="G13" t="n">
-        <v>227629</v>
+        <v>377917</v>
       </c>
       <c r="H13" t="n">
-        <v>37109</v>
+        <v>55831</v>
       </c>
     </row>
     <row r="14">
@@ -714,25 +714,25 @@
         <v>45971</v>
       </c>
       <c r="B14" t="n">
-        <v>1213.73</v>
+        <v>1115.61</v>
       </c>
       <c r="C14" t="n">
-        <v>19.5</v>
+        <v>19.22</v>
       </c>
       <c r="D14" t="n">
-        <v>876.04</v>
+        <v>814.65</v>
       </c>
       <c r="E14" t="n">
-        <v>237.45</v>
+        <v>224.21</v>
       </c>
       <c r="F14" t="n">
-        <v>2035</v>
+        <v>1252</v>
       </c>
       <c r="G14" t="n">
-        <v>304048</v>
+        <v>277424</v>
       </c>
       <c r="H14" t="n">
-        <v>54260</v>
+        <v>46914</v>
       </c>
     </row>
     <row r="15">
@@ -740,25 +740,25 @@
         <v>45972</v>
       </c>
       <c r="B15" t="n">
-        <v>709.0700000000001</v>
+        <v>1178.22</v>
       </c>
       <c r="C15" t="n">
-        <v>10.81</v>
+        <v>18.05</v>
       </c>
       <c r="D15" t="n">
-        <v>515.25</v>
+        <v>860.84</v>
       </c>
       <c r="E15" t="n">
-        <v>137.65</v>
+        <v>228.54</v>
       </c>
       <c r="F15" t="n">
-        <v>1595</v>
+        <v>1608</v>
       </c>
       <c r="G15" t="n">
-        <v>184803</v>
+        <v>300198</v>
       </c>
       <c r="H15" t="n">
-        <v>31252</v>
+        <v>53536</v>
       </c>
     </row>
     <row r="16">
@@ -766,25 +766,25 @@
         <v>45973</v>
       </c>
       <c r="B16" t="n">
-        <v>258.1</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>187.06</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>52.24</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>472</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>81881</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>11552</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -792,25 +792,25 @@
         <v>45974</v>
       </c>
       <c r="B17" t="n">
-        <v>1010.37</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>730.46</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>197.16</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1860</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>286138</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>44076</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -818,25 +818,25 @@
         <v>45975</v>
       </c>
       <c r="B18" t="n">
-        <v>993.42</v>
+        <v>1526.29</v>
       </c>
       <c r="C18" t="n">
-        <v>15.75</v>
+        <v>24</v>
       </c>
       <c r="D18" t="n">
-        <v>719.24</v>
+        <v>1100.63</v>
       </c>
       <c r="E18" t="n">
-        <v>197.34</v>
+        <v>299.68</v>
       </c>
       <c r="F18" t="n">
-        <v>1867</v>
+        <v>1592</v>
       </c>
       <c r="G18" t="n">
-        <v>265826</v>
+        <v>385699</v>
       </c>
       <c r="H18" t="n">
-        <v>44156</v>
+        <v>71374</v>
       </c>
     </row>
     <row r="19">
@@ -844,25 +844,25 @@
         <v>45976</v>
       </c>
       <c r="B19" t="n">
-        <v>972.9</v>
+        <v>1476</v>
       </c>
       <c r="C19" t="n">
-        <v>15.86</v>
+        <v>24</v>
       </c>
       <c r="D19" t="n">
-        <v>705.83</v>
+        <v>1067.92</v>
       </c>
       <c r="E19" t="n">
-        <v>191.1</v>
+        <v>290.05</v>
       </c>
       <c r="F19" t="n">
-        <v>1896</v>
+        <v>1378</v>
       </c>
       <c r="G19" t="n">
-        <v>272080</v>
+        <v>376281</v>
       </c>
       <c r="H19" t="n">
-        <v>42721</v>
+        <v>72371</v>
       </c>
     </row>
     <row r="20">
@@ -870,25 +870,25 @@
         <v>45977</v>
       </c>
       <c r="B20" t="n">
-        <v>1262.07</v>
+        <v>1393.16</v>
       </c>
       <c r="C20" t="n">
-        <v>20.63</v>
+        <v>24</v>
       </c>
       <c r="D20" t="n">
-        <v>915.23</v>
+        <v>1014.58</v>
       </c>
       <c r="E20" t="n">
-        <v>254.86</v>
+        <v>276.18</v>
       </c>
       <c r="F20" t="n">
-        <v>2133</v>
+        <v>1469</v>
       </c>
       <c r="G20" t="n">
-        <v>331093</v>
+        <v>373503</v>
       </c>
       <c r="H20" t="n">
-        <v>59325</v>
+        <v>64515</v>
       </c>
     </row>
     <row r="21">
@@ -896,25 +896,25 @@
         <v>45978</v>
       </c>
       <c r="B21" t="n">
-        <v>825.15</v>
+        <v>1482.54</v>
       </c>
       <c r="C21" t="n">
-        <v>13.37</v>
+        <v>24</v>
       </c>
       <c r="D21" t="n">
-        <v>597.6</v>
+        <v>1070.33</v>
       </c>
       <c r="E21" t="n">
-        <v>165.72</v>
+        <v>294.67</v>
       </c>
       <c r="F21" t="n">
-        <v>1465</v>
+        <v>1384</v>
       </c>
       <c r="G21" t="n">
-        <v>235962</v>
+        <v>392061</v>
       </c>
       <c r="H21" t="n">
-        <v>37762</v>
+        <v>68882</v>
       </c>
     </row>
     <row r="22">
@@ -922,25 +922,25 @@
         <v>45979</v>
       </c>
       <c r="B22" t="n">
-        <v>668.48</v>
+        <v>926.26</v>
       </c>
       <c r="C22" t="n">
-        <v>9.98</v>
+        <v>14.57</v>
       </c>
       <c r="D22" t="n">
-        <v>484.73</v>
+        <v>676.66</v>
       </c>
       <c r="E22" t="n">
-        <v>136.65</v>
+        <v>180.53</v>
       </c>
       <c r="F22" t="n">
-        <v>1284</v>
+        <v>1135</v>
       </c>
       <c r="G22" t="n">
-        <v>180791</v>
+        <v>253581</v>
       </c>
       <c r="H22" t="n">
-        <v>27707</v>
+        <v>46485</v>
       </c>
     </row>
     <row r="23">
@@ -948,25 +948,25 @@
         <v>45980</v>
       </c>
       <c r="B23" t="n">
-        <v>703.41</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>11.76</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>509.3</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>139.77</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>1503</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>193549</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>33274</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -974,25 +974,25 @@
         <v>45981</v>
       </c>
       <c r="B24" t="n">
-        <v>318.58</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>5.48</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>230.37</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>62.58</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>570</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>100566</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>15002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1000,25 +1000,25 @@
         <v>45982</v>
       </c>
       <c r="B25" t="n">
-        <v>562.1</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>9.279999999999999</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>404.46</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>110.34</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>1231</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>160545</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>26178</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1026,25 +1026,25 @@
         <v>45983</v>
       </c>
       <c r="B26" t="n">
-        <v>658.05</v>
+        <v>1509.91</v>
       </c>
       <c r="C26" t="n">
-        <v>11.17</v>
+        <v>24</v>
       </c>
       <c r="D26" t="n">
-        <v>482.11</v>
+        <v>1106.37</v>
       </c>
       <c r="E26" t="n">
-        <v>134.79</v>
+        <v>295.22</v>
       </c>
       <c r="F26" t="n">
-        <v>1131</v>
+        <v>1343</v>
       </c>
       <c r="G26" t="n">
-        <v>204243</v>
+        <v>390670</v>
       </c>
       <c r="H26" t="n">
-        <v>31555</v>
+        <v>69682</v>
       </c>
     </row>
     <row r="27">
@@ -1052,25 +1052,25 @@
         <v>45984</v>
       </c>
       <c r="B27" t="n">
-        <v>1576.17</v>
+        <v>1433.49</v>
       </c>
       <c r="C27" t="n">
-        <v>24</v>
+        <v>23.55</v>
       </c>
       <c r="D27" t="n">
-        <v>1140.36</v>
+        <v>1036.11</v>
       </c>
       <c r="E27" t="n">
-        <v>313.58</v>
+        <v>279.04</v>
       </c>
       <c r="F27" t="n">
-        <v>2173</v>
+        <v>1346</v>
       </c>
       <c r="G27" t="n">
-        <v>406039</v>
+        <v>361650</v>
       </c>
       <c r="H27" t="n">
-        <v>71036</v>
+        <v>66950</v>
       </c>
     </row>
     <row r="28">
@@ -1078,25 +1078,25 @@
         <v>45985</v>
       </c>
       <c r="B28" t="n">
-        <v>1479.86</v>
+        <v>1380.77</v>
       </c>
       <c r="C28" t="n">
         <v>24</v>
       </c>
       <c r="D28" t="n">
-        <v>1067.87</v>
+        <v>1006.19</v>
       </c>
       <c r="E28" t="n">
-        <v>303.01</v>
+        <v>268.02</v>
       </c>
       <c r="F28" t="n">
-        <v>2289</v>
+        <v>1597</v>
       </c>
       <c r="G28" t="n">
-        <v>402018</v>
+        <v>382321</v>
       </c>
       <c r="H28" t="n">
-        <v>70253</v>
+        <v>66192</v>
       </c>
     </row>
     <row r="29">
@@ -1104,25 +1104,25 @@
         <v>45986</v>
       </c>
       <c r="B29" t="n">
-        <v>1063.51</v>
+        <v>1508.03</v>
       </c>
       <c r="C29" t="n">
-        <v>17.63</v>
+        <v>24</v>
       </c>
       <c r="D29" t="n">
-        <v>769.2</v>
+        <v>1092.02</v>
       </c>
       <c r="E29" t="n">
-        <v>214.52</v>
+        <v>302.59</v>
       </c>
       <c r="F29" t="n">
-        <v>1926</v>
+        <v>1477</v>
       </c>
       <c r="G29" t="n">
-        <v>300527</v>
+        <v>370805</v>
       </c>
       <c r="H29" t="n">
-        <v>48215</v>
+        <v>69829</v>
       </c>
     </row>
     <row r="30">
@@ -1130,25 +1130,25 @@
         <v>45987</v>
       </c>
       <c r="B30" t="n">
-        <v>672.64</v>
+        <v>1198.6</v>
       </c>
       <c r="C30" t="n">
-        <v>10.06</v>
+        <v>18.57</v>
       </c>
       <c r="D30" t="n">
-        <v>489.1</v>
+        <v>864.29</v>
       </c>
       <c r="E30" t="n">
-        <v>137.27</v>
+        <v>238.94</v>
       </c>
       <c r="F30" t="n">
-        <v>1380</v>
+        <v>1496</v>
       </c>
       <c r="G30" t="n">
-        <v>175848</v>
+        <v>300001</v>
       </c>
       <c r="H30" t="n">
-        <v>30231</v>
+        <v>58198</v>
       </c>
     </row>
     <row r="31">
@@ -1156,25 +1156,25 @@
         <v>45988</v>
       </c>
       <c r="B31" t="n">
-        <v>748.99</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>11.47</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>547.17</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>146.26</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>1571</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>211234</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>32952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -1182,25 +1182,25 @@
         <v>45989</v>
       </c>
       <c r="B32" t="n">
-        <v>1574.36</v>
+        <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>23.7</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>1150.1</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>315.02</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>2360</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>403909</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>65370</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -1208,25 +1208,25 @@
         <v>45990</v>
       </c>
       <c r="B33" t="n">
-        <v>994.62</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>723.77</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>200.24</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>1605</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>286751</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>46762</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -1234,25 +1234,25 @@
         <v>45991</v>
       </c>
       <c r="B34" t="n">
-        <v>941.4299999999999</v>
+        <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>15.34</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>680.47</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>186.11</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>2084</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>279620</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>44266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1262,25 +1262,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>27378.71</v>
+        <v>23678.5</v>
       </c>
       <c r="C36" t="n">
-        <v>438.6</v>
+        <v>385.7</v>
       </c>
       <c r="D36" t="n">
-        <v>19846.41</v>
+        <v>17181.94</v>
       </c>
       <c r="E36" t="n">
-        <v>5457.8</v>
+        <v>4681.33</v>
       </c>
       <c r="F36" t="n">
-        <v>48428</v>
+        <v>24619</v>
       </c>
       <c r="G36" t="n">
-        <v>7522637</v>
+        <v>6236909</v>
       </c>
       <c r="H36" t="n">
-        <v>1242100</v>
+        <v>1099661</v>
       </c>
     </row>
   </sheetData>

--- a/00-esmagadora-modelo/dados_sujos/apontamentos_mensais/producao_2025_11.xlsx
+++ b/00-esmagadora-modelo/dados_sujos/apontamentos_mensais/producao_2025_11.xlsx
@@ -480,25 +480,25 @@
         <v>45962</v>
       </c>
       <c r="B5" t="n">
-        <v>1414.06</v>
+        <v>1299.25</v>
       </c>
       <c r="C5" t="n">
-        <v>24</v>
+        <v>21.89</v>
       </c>
       <c r="D5" t="n">
-        <v>1031.04</v>
+        <v>932.7</v>
       </c>
       <c r="E5" t="n">
-        <v>291.85</v>
+        <v>259.67</v>
       </c>
       <c r="F5" t="n">
-        <v>1408</v>
+        <v>1335</v>
       </c>
       <c r="G5" t="n">
-        <v>375695</v>
+        <v>354755</v>
       </c>
       <c r="H5" t="n">
-        <v>64084</v>
+        <v>58871</v>
       </c>
     </row>
     <row r="6">
@@ -506,25 +506,25 @@
         <v>45963</v>
       </c>
       <c r="B6" t="n">
-        <v>396.08</v>
+        <v>1254.04</v>
       </c>
       <c r="C6" t="n">
-        <v>6.35</v>
+        <v>20.49</v>
       </c>
       <c r="D6" t="n">
-        <v>286.5</v>
+        <v>911.67</v>
       </c>
       <c r="E6" t="n">
-        <v>78.05</v>
+        <v>255.93</v>
       </c>
       <c r="F6" t="n">
-        <v>494</v>
+        <v>1130</v>
       </c>
       <c r="G6" t="n">
-        <v>116115</v>
+        <v>333039</v>
       </c>
       <c r="H6" t="n">
-        <v>18346</v>
+        <v>56489</v>
       </c>
     </row>
     <row r="7">
@@ -532,25 +532,25 @@
         <v>45964</v>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>1229.35</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>20.34</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>901.95</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>239.77</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1355</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>347743</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>56882</v>
       </c>
     </row>
     <row r="8">
@@ -610,25 +610,25 @@
         <v>45967</v>
       </c>
       <c r="B10" t="n">
-        <v>1473.13</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1070.12</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>289.57</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1555</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>408543</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>67339</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -636,25 +636,25 @@
         <v>45968</v>
       </c>
       <c r="B11" t="n">
-        <v>1493.9</v>
+        <v>1463.53</v>
       </c>
       <c r="C11" t="n">
         <v>24</v>
       </c>
       <c r="D11" t="n">
-        <v>1078.31</v>
+        <v>1054.83</v>
       </c>
       <c r="E11" t="n">
-        <v>293.82</v>
+        <v>297.55</v>
       </c>
       <c r="F11" t="n">
-        <v>1370</v>
+        <v>1424</v>
       </c>
       <c r="G11" t="n">
-        <v>409560</v>
+        <v>370635</v>
       </c>
       <c r="H11" t="n">
-        <v>67993</v>
+        <v>66085</v>
       </c>
     </row>
     <row r="12">
@@ -662,25 +662,25 @@
         <v>45969</v>
       </c>
       <c r="B12" t="n">
-        <v>1473.48</v>
+        <v>1496.14</v>
       </c>
       <c r="C12" t="n">
         <v>24</v>
       </c>
       <c r="D12" t="n">
-        <v>1067.84</v>
+        <v>1092.8</v>
       </c>
       <c r="E12" t="n">
-        <v>292.55</v>
+        <v>289.7</v>
       </c>
       <c r="F12" t="n">
-        <v>1270</v>
+        <v>1322</v>
       </c>
       <c r="G12" t="n">
-        <v>384885</v>
+        <v>424236</v>
       </c>
       <c r="H12" t="n">
-        <v>71140</v>
+        <v>66961</v>
       </c>
     </row>
     <row r="13">
@@ -688,25 +688,25 @@
         <v>45970</v>
       </c>
       <c r="B13" t="n">
-        <v>1298.97</v>
+        <v>1475.58</v>
       </c>
       <c r="C13" t="n">
-        <v>21.39</v>
+        <v>24</v>
       </c>
       <c r="D13" t="n">
-        <v>937.54</v>
+        <v>1072.53</v>
       </c>
       <c r="E13" t="n">
-        <v>257.82</v>
+        <v>288.59</v>
       </c>
       <c r="F13" t="n">
-        <v>1445</v>
+        <v>1332</v>
       </c>
       <c r="G13" t="n">
-        <v>377917</v>
+        <v>411048</v>
       </c>
       <c r="H13" t="n">
-        <v>55831</v>
+        <v>68912</v>
       </c>
     </row>
     <row r="14">
@@ -714,25 +714,25 @@
         <v>45971</v>
       </c>
       <c r="B14" t="n">
-        <v>1115.61</v>
+        <v>1340.37</v>
       </c>
       <c r="C14" t="n">
-        <v>19.22</v>
+        <v>22.19</v>
       </c>
       <c r="D14" t="n">
-        <v>814.65</v>
+        <v>974.74</v>
       </c>
       <c r="E14" t="n">
-        <v>224.21</v>
+        <v>268.53</v>
       </c>
       <c r="F14" t="n">
-        <v>1252</v>
+        <v>965</v>
       </c>
       <c r="G14" t="n">
-        <v>277424</v>
+        <v>355021</v>
       </c>
       <c r="H14" t="n">
-        <v>46914</v>
+        <v>64629</v>
       </c>
     </row>
     <row r="15">
@@ -740,25 +740,25 @@
         <v>45972</v>
       </c>
       <c r="B15" t="n">
-        <v>1178.22</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>18.05</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>860.84</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>228.54</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1608</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>300198</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>53536</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -792,25 +792,25 @@
         <v>45974</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>1452.75</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>1058.07</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>294.32</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1390</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>398296</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>68858</v>
       </c>
     </row>
     <row r="18">
@@ -818,25 +818,25 @@
         <v>45975</v>
       </c>
       <c r="B18" t="n">
-        <v>1526.29</v>
+        <v>1502.25</v>
       </c>
       <c r="C18" t="n">
         <v>24</v>
       </c>
       <c r="D18" t="n">
-        <v>1100.63</v>
+        <v>1079.71</v>
       </c>
       <c r="E18" t="n">
-        <v>299.68</v>
+        <v>300.91</v>
       </c>
       <c r="F18" t="n">
-        <v>1592</v>
+        <v>1415</v>
       </c>
       <c r="G18" t="n">
-        <v>385699</v>
+        <v>430300</v>
       </c>
       <c r="H18" t="n">
-        <v>71374</v>
+        <v>70133</v>
       </c>
     </row>
     <row r="19">
@@ -844,25 +844,25 @@
         <v>45976</v>
       </c>
       <c r="B19" t="n">
-        <v>1476</v>
+        <v>1483.53</v>
       </c>
       <c r="C19" t="n">
         <v>24</v>
       </c>
       <c r="D19" t="n">
-        <v>1067.92</v>
+        <v>1076.28</v>
       </c>
       <c r="E19" t="n">
-        <v>290.05</v>
+        <v>298.14</v>
       </c>
       <c r="F19" t="n">
-        <v>1378</v>
+        <v>1421</v>
       </c>
       <c r="G19" t="n">
-        <v>376281</v>
+        <v>387879</v>
       </c>
       <c r="H19" t="n">
-        <v>72371</v>
+        <v>67759</v>
       </c>
     </row>
     <row r="20">
@@ -870,25 +870,25 @@
         <v>45977</v>
       </c>
       <c r="B20" t="n">
-        <v>1393.16</v>
+        <v>1229.54</v>
       </c>
       <c r="C20" t="n">
-        <v>24</v>
+        <v>19.62</v>
       </c>
       <c r="D20" t="n">
-        <v>1014.58</v>
+        <v>892.64</v>
       </c>
       <c r="E20" t="n">
-        <v>276.18</v>
+        <v>247.04</v>
       </c>
       <c r="F20" t="n">
-        <v>1469</v>
+        <v>1657</v>
       </c>
       <c r="G20" t="n">
-        <v>373503</v>
+        <v>336585</v>
       </c>
       <c r="H20" t="n">
-        <v>64515</v>
+        <v>56850</v>
       </c>
     </row>
     <row r="21">
@@ -896,25 +896,25 @@
         <v>45978</v>
       </c>
       <c r="B21" t="n">
-        <v>1482.54</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>1070.33</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>294.67</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>1384</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>392061</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>68882</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -922,25 +922,25 @@
         <v>45979</v>
       </c>
       <c r="B22" t="n">
-        <v>926.26</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>14.57</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>676.66</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>180.53</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>1135</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>253581</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>46485</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1000,25 +1000,25 @@
         <v>45982</v>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>661.46</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>10.62</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>480.23</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>129.95</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>749</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>193471</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>28291</v>
       </c>
     </row>
     <row r="26">
@@ -1026,25 +1026,25 @@
         <v>45983</v>
       </c>
       <c r="B26" t="n">
-        <v>1509.91</v>
+        <v>1155.64</v>
       </c>
       <c r="C26" t="n">
-        <v>24</v>
+        <v>20.17</v>
       </c>
       <c r="D26" t="n">
-        <v>1106.37</v>
+        <v>834.7</v>
       </c>
       <c r="E26" t="n">
-        <v>295.22</v>
+        <v>226.74</v>
       </c>
       <c r="F26" t="n">
-        <v>1343</v>
+        <v>850</v>
       </c>
       <c r="G26" t="n">
-        <v>390670</v>
+        <v>298477</v>
       </c>
       <c r="H26" t="n">
-        <v>69682</v>
+        <v>53168</v>
       </c>
     </row>
     <row r="27">
@@ -1052,25 +1052,25 @@
         <v>45984</v>
       </c>
       <c r="B27" t="n">
-        <v>1433.49</v>
+        <v>1515.72</v>
       </c>
       <c r="C27" t="n">
-        <v>23.55</v>
+        <v>24</v>
       </c>
       <c r="D27" t="n">
-        <v>1036.11</v>
+        <v>1104.34</v>
       </c>
       <c r="E27" t="n">
-        <v>279.04</v>
+        <v>302.85</v>
       </c>
       <c r="F27" t="n">
-        <v>1346</v>
+        <v>1422</v>
       </c>
       <c r="G27" t="n">
-        <v>361650</v>
+        <v>420175</v>
       </c>
       <c r="H27" t="n">
-        <v>66950</v>
+        <v>67340</v>
       </c>
     </row>
     <row r="28">
@@ -1078,25 +1078,25 @@
         <v>45985</v>
       </c>
       <c r="B28" t="n">
-        <v>1380.77</v>
+        <v>1596.77</v>
       </c>
       <c r="C28" t="n">
         <v>24</v>
       </c>
       <c r="D28" t="n">
-        <v>1006.19</v>
+        <v>1149.72</v>
       </c>
       <c r="E28" t="n">
-        <v>268.02</v>
+        <v>322.57</v>
       </c>
       <c r="F28" t="n">
-        <v>1597</v>
+        <v>1457</v>
       </c>
       <c r="G28" t="n">
-        <v>382321</v>
+        <v>384016</v>
       </c>
       <c r="H28" t="n">
-        <v>66192</v>
+        <v>67677</v>
       </c>
     </row>
     <row r="29">
@@ -1104,25 +1104,25 @@
         <v>45986</v>
       </c>
       <c r="B29" t="n">
-        <v>1508.03</v>
+        <v>1192.51</v>
       </c>
       <c r="C29" t="n">
-        <v>24</v>
+        <v>18.97</v>
       </c>
       <c r="D29" t="n">
-        <v>1092.02</v>
+        <v>864.46</v>
       </c>
       <c r="E29" t="n">
-        <v>302.59</v>
+        <v>232.62</v>
       </c>
       <c r="F29" t="n">
-        <v>1477</v>
+        <v>1321</v>
       </c>
       <c r="G29" t="n">
-        <v>370805</v>
+        <v>313672</v>
       </c>
       <c r="H29" t="n">
-        <v>69829</v>
+        <v>52127</v>
       </c>
     </row>
     <row r="30">
@@ -1130,25 +1130,25 @@
         <v>45987</v>
       </c>
       <c r="B30" t="n">
-        <v>1198.6</v>
+        <v>997.91</v>
       </c>
       <c r="C30" t="n">
-        <v>18.57</v>
+        <v>16.29</v>
       </c>
       <c r="D30" t="n">
-        <v>864.29</v>
+        <v>725.05</v>
       </c>
       <c r="E30" t="n">
-        <v>238.94</v>
+        <v>195.87</v>
       </c>
       <c r="F30" t="n">
-        <v>1496</v>
+        <v>1068</v>
       </c>
       <c r="G30" t="n">
-        <v>300001</v>
+        <v>274380</v>
       </c>
       <c r="H30" t="n">
-        <v>58198</v>
+        <v>42382</v>
       </c>
     </row>
     <row r="31">
@@ -1234,25 +1234,25 @@
         <v>45991</v>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>1429.88</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>1039.39</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>284.25</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>1423</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>408342</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>65030</v>
       </c>
     </row>
     <row r="36">
@@ -1262,25 +1262,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>23678.5</v>
+        <v>23776.22</v>
       </c>
       <c r="C36" t="n">
-        <v>385.7</v>
+        <v>386.58</v>
       </c>
       <c r="D36" t="n">
-        <v>17181.94</v>
+        <v>17245.81</v>
       </c>
       <c r="E36" t="n">
-        <v>4681.33</v>
+        <v>4735</v>
       </c>
       <c r="F36" t="n">
-        <v>24619</v>
+        <v>23036</v>
       </c>
       <c r="G36" t="n">
-        <v>6236909</v>
+        <v>6442070</v>
       </c>
       <c r="H36" t="n">
-        <v>1099661</v>
+        <v>1078444</v>
       </c>
     </row>
   </sheetData>
